--- a/artfynd/A 20995-2019 artfynd.xlsx
+++ b/artfynd/A 20995-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 20995-2019 artfynd.xlsx
+++ b/artfynd/A 20995-2019 artfynd.xlsx
@@ -7353,7 +7353,7 @@
         <v>117962437</v>
       </c>
       <c r="B58" t="n">
-        <v>91064</v>
+        <v>91066</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>

--- a/artfynd/A 20995-2019 artfynd.xlsx
+++ b/artfynd/A 20995-2019 artfynd.xlsx
@@ -7353,7 +7353,7 @@
         <v>117962437</v>
       </c>
       <c r="B58" t="n">
-        <v>91249</v>
+        <v>91259</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>

--- a/artfynd/A 20995-2019 artfynd.xlsx
+++ b/artfynd/A 20995-2019 artfynd.xlsx
@@ -7353,7 +7353,7 @@
         <v>117962437</v>
       </c>
       <c r="B58" t="n">
-        <v>91259</v>
+        <v>91271</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>

--- a/artfynd/A 20995-2019 artfynd.xlsx
+++ b/artfynd/A 20995-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY58"/>
+  <dimension ref="A1:AY59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7464,6 +7464,108 @@
         </is>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>125600723</v>
+      </c>
+      <c r="B59" t="n">
+        <v>91166</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Jon-Persbäckens naturreservat, Ång</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>716595</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7078323</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 20995-2019 artfynd.xlsx
+++ b/artfynd/A 20995-2019 artfynd.xlsx
@@ -7469,12 +7469,7 @@
         <v>125600723</v>
       </c>
       <c r="B59" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91220</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 20995-2019 artfynd.xlsx
+++ b/artfynd/A 20995-2019 artfynd.xlsx
@@ -7469,7 +7469,7 @@
         <v>125600723</v>
       </c>
       <c r="B59" t="n">
-        <v>91220</v>
+        <v>91227</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 20995-2019 artfynd.xlsx
+++ b/artfynd/A 20995-2019 artfynd.xlsx
@@ -7469,7 +7469,7 @@
         <v>125600723</v>
       </c>
       <c r="B59" t="n">
-        <v>91227</v>
+        <v>91228</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 20995-2019 artfynd.xlsx
+++ b/artfynd/A 20995-2019 artfynd.xlsx
@@ -7469,7 +7469,7 @@
         <v>125600723</v>
       </c>
       <c r="B59" t="n">
-        <v>91228</v>
+        <v>91232</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 20995-2019 artfynd.xlsx
+++ b/artfynd/A 20995-2019 artfynd.xlsx
@@ -7469,7 +7469,7 @@
         <v>125600723</v>
       </c>
       <c r="B59" t="n">
-        <v>91232</v>
+        <v>91234</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 20995-2019 artfynd.xlsx
+++ b/artfynd/A 20995-2019 artfynd.xlsx
@@ -7469,7 +7469,7 @@
         <v>125600723</v>
       </c>
       <c r="B59" t="n">
-        <v>91234</v>
+        <v>91236</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 20995-2019 artfynd.xlsx
+++ b/artfynd/A 20995-2019 artfynd.xlsx
@@ -7469,7 +7469,7 @@
         <v>125600723</v>
       </c>
       <c r="B59" t="n">
-        <v>91236</v>
+        <v>91238</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
